--- a/外网端源码/H楼交接班日志空模板.xlsx
+++ b/外网端源码/H楼交接班日志空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="H楼" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="91">
   <si>
     <t>南通数据中心H楼交接班日志</t>
   </si>
@@ -65,7 +65,10 @@
     <t>空调编号</t>
   </si>
   <si>
-    <t>配电室/电池室CRAC-01</t>
+    <t>配电室CRAC-01</t>
+  </si>
+  <si>
+    <t>电池室CRAC-01</t>
   </si>
   <si>
     <t>H楼UPS-2负载率（%）</t>
@@ -309,7 +312,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -360,13 +363,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1066,148 +1062,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1648,16 +1644,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="17.4545454545455" customWidth="1"/>
-    <col min="3" max="3" width="24.1818181818182" customWidth="1"/>
-    <col min="4" max="4" width="21.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="22.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="24.2727272727273" customWidth="1"/>
-    <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
-    <col min="8" max="8" width="22.4545454545455" customWidth="1"/>
+    <col min="2" max="2" width="17.4537037037037" customWidth="1"/>
+    <col min="3" max="3" width="24.1851851851852" customWidth="1"/>
+    <col min="4" max="4" width="21.2685185185185" customWidth="1"/>
+    <col min="5" max="5" width="22.8148148148148" customWidth="1"/>
+    <col min="6" max="6" width="24.2685185185185" customWidth="1"/>
+    <col min="7" max="7" width="24.6388888888889" customWidth="1"/>
+    <col min="8" max="8" width="22.4537037037037" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:8">
@@ -1777,12 +1773,12 @@
         <v>12</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>9</v>
@@ -1790,7 +1786,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="6"/>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4">
@@ -1802,7 +1798,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4">
         <v>130</v>
@@ -1810,7 +1806,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="6"/>
       <c r="E9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
@@ -1822,7 +1818,7 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:8">
       <c r="A10" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1834,7 +1830,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:8">
       <c r="A11" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1846,25 +1842,25 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>2</v>
@@ -1872,7 +1868,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:8">
       <c r="A13" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1884,31 +1880,31 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
       <c r="H14" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -1920,13 +1916,13 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1938,7 +1934,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:8">
       <c r="A17" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1950,24 +1946,24 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:8">
@@ -1975,26 +1971,26 @@
         <v>1</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:8">
       <c r="A20" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2006,22 +2002,22 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:8">
       <c r="A21" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="19"/>
       <c r="F21" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:8">
@@ -2029,24 +2025,24 @@
         <v>1</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11"/>
       <c r="F22" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:8">
       <c r="A23" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2058,22 +2054,22 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="6"/>
       <c r="F24" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:8">
@@ -2081,24 +2077,24 @@
         <v>1</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="6"/>
       <c r="F25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:8">
       <c r="A26" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2110,26 +2106,26 @@
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:8">
@@ -2137,28 +2133,28 @@
         <v>1</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:8">
       <c r="A29" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2170,23 +2166,23 @@
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H30" s="6"/>
     </row>
@@ -2195,26 +2191,26 @@
         <v>1</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H31" s="19"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:8">
       <c r="A32" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -2226,20 +2222,20 @@
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="6"/>
       <c r="F33" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:8">
@@ -2247,22 +2243,22 @@
         <v>1</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="6"/>
       <c r="F34" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:8">
       <c r="A35" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -2274,20 +2270,20 @@
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:8">
       <c r="A36" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="19"/>
       <c r="F36" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G36" s="19"/>
       <c r="H36" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:8">
@@ -2295,22 +2291,22 @@
         <v>1</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
       <c r="E37" s="19"/>
       <c r="F37" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:8">
       <c r="A38" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2322,10 +2318,10 @@
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -2333,7 +2329,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="6"/>
       <c r="H39" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:8">
@@ -2341,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -2357,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -2373,7 +2369,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -2386,7 +2382,7 @@
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:8">
       <c r="A43" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2398,45 +2394,45 @@
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:8">
       <c r="A44" s="23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="1:8">
       <c r="A45" s="32"/>
       <c r="B45" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>2</v>
@@ -2445,20 +2441,20 @@
     <row r="46" ht="18" customHeight="1" spans="1:8">
       <c r="A46" s="32"/>
       <c r="B46" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>2</v>
@@ -2467,20 +2463,20 @@
     <row r="47" ht="18" customHeight="1" spans="1:8">
       <c r="A47" s="32"/>
       <c r="B47" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" s="8" t="s">
         <v>2</v>
@@ -2489,20 +2485,20 @@
     <row r="48" ht="18" customHeight="1" spans="1:8">
       <c r="A48" s="10"/>
       <c r="B48" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" s="33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>2</v>
@@ -2510,16 +2506,16 @@
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:8">
       <c r="A49" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6"/>
       <c r="F49" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="6"/>
@@ -2532,7 +2528,7 @@
       <c r="E50" s="35"/>
       <c r="F50" s="36"/>
       <c r="G50" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" s="35"/>
     </row>
